--- a/Unity/Assets/Config/Excel/RechargePointsRewardConfig.xlsx
+++ b/Unity/Assets/Config/Excel/RechargePointsRewardConfig.xlsx
@@ -89,7 +89,7 @@
     <t>10003006;1</t>
   </si>
   <si>
-    <t>10003011;1</t>
+    <t>10003011;1@10001001;1@10001002;1@10003006;1</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1197,7 @@
         <v>10000001</v>
       </c>
       <c r="C4" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>10</v>
@@ -1208,7 +1208,8 @@
         <v>10000002</v>
       </c>
       <c r="C5" s="2">
-        <v>20</v>
+        <f>C4+100</f>
+        <v>200</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>11</v>
@@ -1219,7 +1220,8 @@
         <v>10000003</v>
       </c>
       <c r="C6" s="2">
-        <v>50</v>
+        <f t="shared" ref="C6:C14" si="0">C5+100</f>
+        <v>300</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>12</v>
@@ -1230,8 +1232,8 @@
         <v>10000004</v>
       </c>
       <c r="C7" s="2">
-        <f>C6+50</f>
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>13</v>
@@ -1242,8 +1244,8 @@
         <v>10000005</v>
       </c>
       <c r="C8" s="2">
-        <f t="shared" ref="C8:C14" si="0">C7+50</f>
-        <v>150</v>
+        <f t="shared" si="0"/>
+        <v>500</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>14</v>
@@ -1255,7 +1257,7 @@
       </c>
       <c r="C9" s="2">
         <f t="shared" si="0"/>
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>15</v>
@@ -1267,7 +1269,7 @@
       </c>
       <c r="C10" s="2">
         <f t="shared" si="0"/>
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>16</v>
@@ -1279,7 +1281,7 @@
       </c>
       <c r="C11" s="2">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>17</v>
@@ -1291,7 +1293,7 @@
       </c>
       <c r="C12" s="2">
         <f t="shared" si="0"/>
-        <v>350</v>
+        <v>900</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>18</v>
@@ -1303,7 +1305,7 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" si="0"/>
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>19</v>
@@ -1315,7 +1317,7 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" si="0"/>
-        <v>450</v>
+        <v>1100</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>20</v>

--- a/Unity/Assets/Config/Excel/RechargePointsRewardConfig.xlsx
+++ b/Unity/Assets/Config/Excel/RechargePointsRewardConfig.xlsx
@@ -1313,7 +1313,7 @@
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="1:4">
       <c r="B14" s="2">
-        <v>10002002</v>
+        <v>10000011</v>
       </c>
       <c r="C14" s="2">
         <f t="shared" si="0"/>
